--- a/Grids Germany/No leap years/Saxony insights/[Saxony][Manhattan][CI]Yearly_normality.xlsx
+++ b/Grids Germany/No leap years/Saxony insights/[Saxony][Manhattan][CI]Yearly_normality.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_W</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_p</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P1_Normality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_W</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_p</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>P2_Normality</t>
         </is>
@@ -478,16 +490,16 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9727820754051208</v>
+        <v>0.9765315055847168</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2548757195472717</v>
+        <v>0.3908657133579254</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -495,10 +507,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7642161846160889</v>
+        <v>0.7639173269271851</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006826043827459216</v>
+        <v>0.0009393027285113931</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -516,16 +528,16 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9377564787864685</v>
+        <v>0.9426259994506836</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007522753905504942</v>
+        <v>0.01433847565203905</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -533,10 +545,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.962988555431366</v>
+        <v>0.9621788263320923</v>
       </c>
       <c r="I3" t="n">
-        <v>0.688154399394989</v>
+        <v>0.7014603018760681</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -554,16 +566,16 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9794163703918457</v>
+        <v>0.9779138565063477</v>
       </c>
       <c r="F4" t="n">
-        <v>0.475795179605484</v>
+        <v>0.4414486289024353</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -571,10 +583,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8530420064926147</v>
+        <v>0.8131905794143677</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01193740498274565</v>
+        <v>0.004098793957382441</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -592,16 +604,16 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>0.982293426990509</v>
+        <v>0.973534107208252</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6032741665840149</v>
+        <v>0.2966727316379547</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -609,10 +621,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9309361577033997</v>
+        <v>0.9499180912971497</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2256262004375458</v>
+        <v>0.4883902668952942</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -630,16 +642,16 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>0.928198516368866</v>
+        <v>0.9314395785331726</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003097197506576777</v>
+        <v>0.005104782525449991</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -647,10 +659,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8997534513473511</v>
+        <v>0.8888862133026123</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06728113442659378</v>
+        <v>0.05349041521549225</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -668,16 +680,16 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9824623465538025</v>
+        <v>0.9846429824829102</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6111696362495422</v>
+        <v>0.7354710102081299</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -685,10 +697,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8501062393188477</v>
+        <v>0.8676729798316956</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01076432783156633</v>
+        <v>0.02505945228040218</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -706,16 +718,16 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9851176738739014</v>
+        <v>0.9854990243911743</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7369873523712158</v>
+        <v>0.7739896178245544</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,10 +735,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.9429093599319458</v>
+        <v>0.9319444298744202</v>
       </c>
       <c r="I8" t="n">
-        <v>0.354327917098999</v>
+        <v>0.2616688013076782</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -744,16 +756,16 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9517843723297119</v>
+        <v>0.9444142580032349</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0297689251601696</v>
+        <v>0.01699401251971722</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -761,10 +773,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.9173935651779175</v>
+        <v>0.8936769962310791</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1334146410226822</v>
+        <v>0.06370773166418076</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -782,16 +794,16 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9805710315704346</v>
+        <v>0.9815430641174316</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5251047611236572</v>
+        <v>0.5934456586837769</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -799,10 +811,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8822041749954224</v>
+        <v>0.8859250545501709</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03452854230999947</v>
+        <v>0.04804101586341858</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -820,16 +832,16 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9653497934341431</v>
+        <v>0.9696723222732544</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1197109520435333</v>
+        <v>0.204645648598671</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -837,14 +849,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8945986032485962</v>
+        <v>0.8800345063209534</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05520609766244888</v>
+        <v>0.03885295987129211</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -858,16 +870,16 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9409745335578918</v>
+        <v>0.9378194212913513</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01023667585104704</v>
+        <v>0.009140683338046074</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -875,10 +887,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.9525840878486633</v>
+        <v>0.9791196584701538</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4986493289470673</v>
+        <v>0.9562320113182068</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -896,16 +908,16 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9770790338516235</v>
+        <v>0.9782533645629883</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3854781091213226</v>
+        <v>0.4545459747314453</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -913,10 +925,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.9582836627960205</v>
+        <v>0.9663133025169373</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5994779467582703</v>
+        <v>0.7759369611740112</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -934,16 +946,16 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9632290005683899</v>
+        <v>0.9598944783210754</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09616878628730774</v>
+        <v>0.07744248956441879</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -951,10 +963,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.9574266672134399</v>
+        <v>0.9549083113670349</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5837301015853882</v>
+        <v>0.5711774826049805</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -972,16 +984,16 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9761642813682556</v>
+        <v>0.975578784942627</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3538457155227661</v>
+        <v>0.3586293458938599</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -989,10 +1001,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.9616970419883728</v>
+        <v>0.9586378931999207</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6635701060295105</v>
+        <v>0.6371484994888306</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1010,16 +1022,16 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>0.963726818561554</v>
+        <v>0.9598605632781982</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1012437865138054</v>
+        <v>0.07718033343553543</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1027,10 +1039,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.9351880550384521</v>
+        <v>0.9212027788162231</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2654543817043304</v>
+        <v>0.176368236541748</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1048,16 +1060,16 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9711788892745972</v>
+        <v>0.9751021862030029</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2171564400196075</v>
+        <v>0.343311220407486</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1065,14 +1077,14 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.889872133731842</v>
+        <v>0.8988966345787048</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04610840231180191</v>
+        <v>0.07716663926839828</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1086,16 +1098,16 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9392644166946411</v>
+        <v>0.9445387721061707</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008685898967087269</v>
+        <v>0.01719705946743488</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1103,10 +1115,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.9570789933204651</v>
+        <v>0.9537447690963745</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5773914456367493</v>
+        <v>0.5512301921844482</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1124,16 +1136,16 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9147723913192749</v>
+        <v>0.9248388409614563</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0009528685477562249</v>
+        <v>0.002844976261258125</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1141,10 +1153,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.9588801860809326</v>
+        <v>0.9492099285125732</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6105364561080933</v>
+        <v>0.4772754311561584</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1162,16 +1174,16 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9683269262313843</v>
+        <v>0.9561998248100281</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1625639945268631</v>
+        <v>0.05360531434416771</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1179,10 +1191,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.9469103813171387</v>
+        <v>0.9416232109069824</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4095235168933868</v>
+        <v>0.3693743348121643</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1200,16 +1212,16 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9752563834190369</v>
+        <v>0.9709426164627075</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3245393931865692</v>
+        <v>0.2315729856491089</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1217,10 +1229,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.9435927867889404</v>
+        <v>0.9480168223381042</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3633025586605072</v>
+        <v>0.458937019109726</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1238,27 +1250,27 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9471815228462219</v>
+        <v>0.9622477293014526</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01878424361348152</v>
+        <v>0.09796541929244995</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.9416481256484985</v>
+        <v>0.9390586614608765</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3382526934146881</v>
+        <v>0.3376427888870239</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1276,16 +1288,16 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>0.971750795841217</v>
+        <v>0.9653922915458679</v>
       </c>
       <c r="F23" t="n">
-        <v>0.229986160993576</v>
+        <v>0.134075254201889</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1293,10 +1305,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.9313743114471436</v>
+        <v>0.9335861802101135</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2294566929340363</v>
+        <v>0.2776938676834106</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1314,16 +1326,16 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9188163876533508</v>
+        <v>0.9186289310455322</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00134811969473958</v>
+        <v>0.001668689772486687</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1331,10 +1343,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.8547375202178955</v>
+        <v>0.8393439054489136</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01267596147954464</v>
+        <v>0.009532596915960312</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1352,16 +1364,16 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9848237633705139</v>
+        <v>0.9806709289550781</v>
       </c>
       <c r="F25" t="n">
-        <v>0.723136305809021</v>
+        <v>0.5547695159912109</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1369,10 +1381,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.8347864151000977</v>
+        <v>0.8077554702758789</v>
       </c>
       <c r="I25" t="n">
-        <v>0.006339917425066233</v>
+        <v>0.003458810271695256</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1390,27 +1402,27 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9568353295326233</v>
+        <v>0.9716469645500183</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04976527020335197</v>
+        <v>0.2478642612695694</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.9678972959518433</v>
+        <v>0.9689484238624573</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7806425094604492</v>
+        <v>0.8212993741035461</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1428,16 +1440,16 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9666125774383545</v>
+        <v>0.9586792588233948</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1363425254821777</v>
+        <v>0.06860034912824631</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1445,10 +1457,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.9514954686164856</v>
+        <v>0.9448723196983337</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4805989265441895</v>
+        <v>0.4130268096923828</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1466,16 +1478,16 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9813365340232849</v>
+        <v>0.982466995716095</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5592544674873352</v>
+        <v>0.6354012489318848</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1483,10 +1495,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.934083878993988</v>
+        <v>0.9127305746078491</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2545287907123566</v>
+        <v>0.1287893354892731</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1504,16 +1516,16 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9906067252159119</v>
+        <v>0.9894949197769165</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9473762512207031</v>
+        <v>0.9252224564552307</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1521,10 +1533,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.9164236783981323</v>
+        <v>0.9185649156570435</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1284663826227188</v>
+        <v>0.159941554069519</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1542,16 +1554,16 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9317091107368469</v>
+        <v>0.9293064475059509</v>
       </c>
       <c r="F30" t="n">
-        <v>0.004270256962627172</v>
+        <v>0.004217490553855896</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1559,10 +1571,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.8329916596412659</v>
+        <v>0.8286461234092712</v>
       </c>
       <c r="I30" t="n">
-        <v>0.005965416319668293</v>
+        <v>0.006712428759783506</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1580,16 +1592,16 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9918421506881714</v>
+        <v>0.989932656288147</v>
       </c>
       <c r="F31" t="n">
-        <v>0.972698450088501</v>
+        <v>0.9372492432594299</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1597,10 +1609,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.8689861297607422</v>
+        <v>0.8772674202919006</v>
       </c>
       <c r="I31" t="n">
-        <v>0.02117195911705494</v>
+        <v>0.03519066795706749</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1618,16 +1630,16 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9094552993774414</v>
+        <v>0.9033586978912354</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0006099424208514392</v>
+        <v>0.0004792132240254432</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1635,10 +1647,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.9056002497673035</v>
+        <v>0.9185603857040405</v>
       </c>
       <c r="I32" t="n">
-        <v>0.08433128148317337</v>
+        <v>0.1599146127700806</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1656,16 +1668,16 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9874979853630066</v>
+        <v>0.9870522022247314</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8431412577629089</v>
+        <v>0.8399389386177063</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1673,10 +1685,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.9553610682487488</v>
+        <v>0.947650134563446</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5465558171272278</v>
+        <v>0.4534009993076324</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1694,16 +1706,16 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9685581922531128</v>
+        <v>0.9764247536659241</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1664539575576782</v>
+        <v>0.3871446251869202</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1711,10 +1723,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.9209896922111511</v>
+        <v>0.9103332757949829</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1534768790006638</v>
+        <v>0.1178192719817162</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1732,16 +1744,16 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9824730157852173</v>
+        <v>0.9841735363006592</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6116700172424316</v>
+        <v>0.7139892578125</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1749,10 +1761,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.9596341252326965</v>
+        <v>0.9589037895202637</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6246131658554077</v>
+        <v>0.6419426202774048</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1770,16 +1782,16 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D36" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9638103842735291</v>
+        <v>0.9565056562423706</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1021220237016678</v>
+        <v>0.05525790899991989</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1787,10 +1799,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.9206198453903198</v>
+        <v>0.9242430329322815</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1512826532125473</v>
+        <v>0.1973451226949692</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1808,16 +1820,16 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9845921397209167</v>
+        <v>0.9839194416999817</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7121710777282715</v>
+        <v>0.7023032307624817</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1825,10 +1837,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.9349416494369507</v>
+        <v>0.9240543842315674</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2629798650741577</v>
+        <v>0.1959762126207352</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1846,16 +1858,16 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E38" t="n">
-        <v>0.964120626449585</v>
+        <v>0.9634139537811279</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1054472699761391</v>
+        <v>0.1100690215826035</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1863,10 +1875,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.9125778675079346</v>
+        <v>0.9255653023719788</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1105925440788269</v>
+        <v>0.2072015553712845</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1884,16 +1896,16 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9691362380981445</v>
+        <v>0.9666784405708313</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1765674650669098</v>
+        <v>0.1523567140102386</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1901,10 +1913,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.9396290183067322</v>
+        <v>0.9434834122657776</v>
       </c>
       <c r="I39" t="n">
-        <v>0.313812792301178</v>
+        <v>0.3938923478126526</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1922,16 +1934,16 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9694213271141052</v>
+        <v>0.972260057926178</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1817689538002014</v>
+        <v>0.262877881526947</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1939,10 +1951,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.8908385634422302</v>
+        <v>0.873677134513855</v>
       </c>
       <c r="I40" t="n">
-        <v>0.04783261194825172</v>
+        <v>0.03097055293619633</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1960,16 +1972,16 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9693796634674072</v>
+        <v>0.9627598524093628</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1810002624988556</v>
+        <v>0.1031084582209587</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1977,10 +1989,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.9148586392402649</v>
+        <v>0.906059741973877</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1208662241697311</v>
+        <v>0.1005479618906975</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1998,27 +2010,27 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9549972414970398</v>
+        <v>0.9575827121734619</v>
       </c>
       <c r="F42" t="n">
-        <v>0.04124036431312561</v>
+        <v>0.06150255724787712</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.9617992639541626</v>
+        <v>0.967334508895874</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6655129790306091</v>
+        <v>0.7938032150268555</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2036,16 +2048,16 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9554347395896912</v>
+        <v>0.9455996751785278</v>
       </c>
       <c r="F43" t="n">
-        <v>0.04312288016080856</v>
+        <v>0.01903335191309452</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2053,10 +2065,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.9677733182907104</v>
+        <v>0.9643886685371399</v>
       </c>
       <c r="I43" t="n">
-        <v>0.778363823890686</v>
+        <v>0.7415676116943359</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2074,16 +2086,16 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D44" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9713484048843384</v>
+        <v>0.9692093729972839</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2208894044160843</v>
+        <v>0.1955780833959579</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2091,10 +2103,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.9363574385643005</v>
+        <v>0.9156054258346558</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2774912714958191</v>
+        <v>0.1433022171258926</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2112,16 +2124,16 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9821358323097229</v>
+        <v>0.9784833192825317</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5959408283233643</v>
+        <v>0.4635631740093231</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2129,10 +2141,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.9524220824241638</v>
+        <v>0.941649317741394</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4959359467029572</v>
+        <v>0.3697097897529602</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2150,16 +2162,16 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9627779722213745</v>
+        <v>0.9617271423339844</v>
       </c>
       <c r="F46" t="n">
-        <v>0.09178953617811203</v>
+        <v>0.09299928694963455</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2167,10 +2179,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.9054743647575378</v>
+        <v>0.8895425200462341</v>
       </c>
       <c r="I46" t="n">
-        <v>0.08392090350389481</v>
+        <v>0.05478310585021973</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2188,16 +2200,16 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9750199913978577</v>
+        <v>0.9748975038528442</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3172455728054047</v>
+        <v>0.3368997573852539</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2205,10 +2217,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.945809543132782</v>
+        <v>0.9501733183860779</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3936969637870789</v>
+        <v>0.4924376308917999</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2226,16 +2238,16 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D48" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9811010956764221</v>
+        <v>0.9832060933113098</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5486405491828918</v>
+        <v>0.669397234916687</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2243,10 +2255,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.9589893817901611</v>
+        <v>0.9676567316055298</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6125680804252625</v>
+        <v>0.7993713617324829</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2264,16 +2276,16 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9761326909065247</v>
+        <v>0.9738466739654541</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3527894914150238</v>
+        <v>0.3055151402950287</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2281,10 +2293,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.9178592562675476</v>
+        <v>0.935055136680603</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1358581185340881</v>
+        <v>0.2927797138690948</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2302,16 +2314,16 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9802824854850769</v>
+        <v>0.9803869128227234</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5125197172164917</v>
+        <v>0.5424250364303589</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2319,10 +2331,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.970167875289917</v>
+        <v>0.9651678800582886</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8213821053504944</v>
+        <v>0.7555718421936035</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2340,16 +2352,16 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9792050123214722</v>
+        <v>0.9759780168533325</v>
       </c>
       <c r="F51" t="n">
-        <v>0.46708744764328</v>
+        <v>0.3718738853931427</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2357,10 +2369,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.9453458189964294</v>
+        <v>0.9503085613250732</v>
       </c>
       <c r="I51" t="n">
-        <v>0.387175589799881</v>
+        <v>0.4945913851261139</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2378,16 +2390,16 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9728357791900635</v>
+        <v>0.975003182888031</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2562370896339417</v>
+        <v>0.3401976525783539</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2395,10 +2407,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.9411562085151672</v>
+        <v>0.9374821782112122</v>
       </c>
       <c r="I52" t="n">
-        <v>0.332152783870697</v>
+        <v>0.3193088471889496</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2416,16 +2428,16 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9684383869171143</v>
+        <v>0.9633466005325317</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1644270569086075</v>
+        <v>0.1093312501907349</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2433,10 +2445,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.9199339151382446</v>
+        <v>0.9161632657051086</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1472947895526886</v>
+        <v>0.1463015526533127</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2454,16 +2466,16 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D54" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9741264581680298</v>
+        <v>0.9728431105613708</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2909187972545624</v>
+        <v>0.2779006958007812</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2471,10 +2483,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.9236547946929932</v>
+        <v>0.9098905324935913</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1702418923377991</v>
+        <v>0.1158987209200859</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2492,16 +2504,16 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9756834506988525</v>
+        <v>0.9683753848075867</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3380669951438904</v>
+        <v>0.1801874488592148</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2509,10 +2521,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9768479466438293</v>
+        <v>0.9607601165771484</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9230896234512329</v>
+        <v>0.6756128072738647</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2530,16 +2542,16 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9677962064743042</v>
+        <v>0.9675450921058655</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1539652049541473</v>
+        <v>0.1660109907388687</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2547,10 +2559,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.9298040866851807</v>
+        <v>0.9374420642852783</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2160065770149231</v>
+        <v>0.3188537061214447</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2568,16 +2580,16 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D57" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9778427481651306</v>
+        <v>0.9825976490974426</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4135082066059113</v>
+        <v>0.6413921713829041</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2585,10 +2597,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.9569483399391174</v>
+        <v>0.9681870341300964</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5750182867050171</v>
+        <v>0.8084543347358704</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2606,16 +2618,16 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D58" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9445378184318542</v>
+        <v>0.9416728019714355</v>
       </c>
       <c r="F58" t="n">
-        <v>0.01447520311921835</v>
+        <v>0.01310387160629034</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2623,10 +2635,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.9433432221412659</v>
+        <v>0.9618805646896362</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3600037395954132</v>
+        <v>0.6960260272026062</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2644,27 +2656,27 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9611249566078186</v>
+        <v>0.9554242491722107</v>
       </c>
       <c r="F59" t="n">
-        <v>0.07738259434700012</v>
+        <v>0.04963767156004906</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.9487196207046509</v>
+        <v>0.938267707824707</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4365872740745544</v>
+        <v>0.3283340632915497</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2682,16 +2694,16 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D60" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9804403185844421</v>
+        <v>0.9791797995567322</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5193830132484436</v>
+        <v>0.4915734529495239</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2699,10 +2711,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.9325103759765625</v>
+        <v>0.940463125705719</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2396747171878815</v>
+        <v>0.3547253012657166</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2720,16 +2732,16 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D61" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9542226791381836</v>
+        <v>0.9476280808448792</v>
       </c>
       <c r="F61" t="n">
-        <v>0.03811194375157356</v>
+        <v>0.02313561178743839</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2737,10 +2749,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.9544257521629333</v>
+        <v>0.96279376745224</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5301362276077271</v>
+        <v>0.712658166885376</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2758,16 +2770,16 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D62" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9085341691970825</v>
+        <v>0.9170625805854797</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0005652192048728466</v>
+        <v>0.001462179934605956</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2775,10 +2787,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.9746280312538147</v>
+        <v>0.978609025478363</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8931726217269897</v>
+        <v>0.9515984058380127</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2796,16 +2808,16 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D63" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9793525338172913</v>
+        <v>0.9783797264099121</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4731549322605133</v>
+        <v>0.4594874978065491</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2813,10 +2825,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.9180859923362732</v>
+        <v>0.9005009531974792</v>
       </c>
       <c r="I63" t="n">
-        <v>0.137063667178154</v>
+        <v>0.08186721056699753</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2834,16 +2846,16 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D64" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9488672018051147</v>
+        <v>0.9508059620857239</v>
       </c>
       <c r="F64" t="n">
-        <v>0.02221322245895863</v>
+        <v>0.03150628134608269</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2851,10 +2863,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.9538306593894958</v>
+        <v>0.9443641304969788</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5198360085487366</v>
+        <v>0.4059431850910187</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2872,16 +2884,16 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D65" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9663195013999939</v>
+        <v>0.9683033227920532</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1322919577360153</v>
+        <v>0.1789130121469498</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2889,10 +2901,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.9793287515640259</v>
+        <v>0.9825056791305542</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9507513642311096</v>
+        <v>0.9802992939949036</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2910,16 +2922,16 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D66" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9530252814292908</v>
+        <v>0.9415895938873291</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0337490439414978</v>
+        <v>0.01300149969756603</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2927,10 +2939,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.9882171154022217</v>
+        <v>0.9842266440391541</v>
       </c>
       <c r="I66" t="n">
-        <v>0.9972235560417175</v>
+        <v>0.9882636070251465</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2948,16 +2960,16 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D67" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9110517501831055</v>
+        <v>0.9156925082206726</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0006965395878069103</v>
+        <v>0.001303651835769415</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2965,10 +2977,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.9782326817512512</v>
+        <v>0.9852860569953918</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9393275380134583</v>
+        <v>0.9918859004974365</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2986,16 +2998,16 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D68" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9647674560546875</v>
+        <v>0.9581570029258728</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1127304062247276</v>
+        <v>0.0651218593120575</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3003,10 +3015,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.954287588596344</v>
+        <v>0.9606914520263672</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5277349948883057</v>
+        <v>0.67436283826828</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3024,16 +3036,16 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D69" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9694398045539856</v>
+        <v>0.9720808267593384</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1821112632751465</v>
+        <v>0.2584078013896942</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3041,10 +3053,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.8989905118942261</v>
+        <v>0.9615206122398376</v>
       </c>
       <c r="I69" t="n">
-        <v>0.06533445417881012</v>
+        <v>0.6894658803939819</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3062,16 +3074,16 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D70" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9636042714118958</v>
+        <v>0.9611893892288208</v>
       </c>
       <c r="F70" t="n">
-        <v>0.09997007995843887</v>
+        <v>0.08813447505235672</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3079,10 +3091,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.7906654477119446</v>
+        <v>0.7770781517028809</v>
       </c>
       <c r="I70" t="n">
-        <v>0.001515184761956334</v>
+        <v>0.001372897415421903</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3100,16 +3112,16 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D71" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9451964497566223</v>
+        <v>0.9366168975830078</v>
       </c>
       <c r="F71" t="n">
-        <v>0.01544183399528265</v>
+        <v>0.008179371245205402</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3117,10 +3129,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.9381880760192871</v>
+        <v>0.9284336566925049</v>
       </c>
       <c r="I71" t="n">
-        <v>0.2973251342773438</v>
+        <v>0.2302221059799194</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3138,16 +3150,16 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D72" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9294084310531616</v>
+        <v>0.9345270395278931</v>
       </c>
       <c r="F72" t="n">
-        <v>0.003457568353042006</v>
+        <v>0.006752730347216129</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3155,10 +3167,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.6974054574966431</v>
+        <v>0.6942651271820068</v>
       </c>
       <c r="I72" t="n">
-        <v>0.000108053587609902</v>
+        <v>0.000146002639667131</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3176,16 +3188,16 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D73" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9607755541801453</v>
+        <v>0.957116425037384</v>
       </c>
       <c r="F73" t="n">
-        <v>0.07464141398668289</v>
+        <v>0.05871527642011642</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3193,10 +3205,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.963736891746521</v>
+        <v>0.9601743221282959</v>
       </c>
       <c r="I73" t="n">
-        <v>0.702414870262146</v>
+        <v>0.664957582950592</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3214,16 +3226,16 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D74" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9289314746856689</v>
+        <v>0.9263449907302856</v>
       </c>
       <c r="F74" t="n">
-        <v>0.003310498548671603</v>
+        <v>0.003245742758736014</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3231,14 +3243,14 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.8866851925849915</v>
+        <v>0.8929988145828247</v>
       </c>
       <c r="I74" t="n">
-        <v>0.04086747020483017</v>
+        <v>0.06214622408151627</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3252,16 +3264,16 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9720311164855957</v>
+        <v>0.9762313365936279</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2365231513977051</v>
+        <v>0.3804749846458435</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3269,10 +3281,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.8666242361068726</v>
+        <v>0.8494352102279663</v>
       </c>
       <c r="I75" t="n">
-        <v>0.01942589320242405</v>
+        <v>0.01336622983217239</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3290,16 +3302,16 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D76" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9677978754043579</v>
+        <v>0.9710869789123535</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1539915055036545</v>
+        <v>0.2348297238349915</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3307,10 +3319,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.9676394462585449</v>
+        <v>0.9632589817047119</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7758979797363281</v>
+        <v>0.7211147546768188</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3328,16 +3340,16 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9689183831214905</v>
+        <v>0.9705429673194885</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1726894229650497</v>
+        <v>0.2227679342031479</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3345,10 +3357,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.9559691548347473</v>
+        <v>0.9544664025306702</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5573748350143433</v>
+        <v>0.5635603070259094</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3366,16 +3378,16 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D78" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9504167437553406</v>
+        <v>0.946657657623291</v>
       </c>
       <c r="F78" t="n">
-        <v>0.02594045177102089</v>
+        <v>0.02106902934610844</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3383,10 +3395,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.970832347869873</v>
+        <v>0.9667409658432007</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8328690528869629</v>
+        <v>0.7834563255310059</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3404,16 +3416,16 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D79" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9415721893310547</v>
+        <v>0.9406483173370361</v>
       </c>
       <c r="F79" t="n">
-        <v>0.01084494218230247</v>
+        <v>0.01190012414008379</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3421,10 +3433,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.9477003812789917</v>
+        <v>0.9586796760559082</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4211809635162354</v>
+        <v>0.6379021406173706</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3442,16 +3454,16 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D80" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9842804670333862</v>
+        <v>0.9812256693840027</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6973630785942078</v>
+        <v>0.5792466402053833</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3459,10 +3471,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.964765727519989</v>
+        <v>0.9684897661209106</v>
       </c>
       <c r="I80" t="n">
-        <v>0.7219867706298828</v>
+        <v>0.8135905265808105</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3480,16 +3492,16 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D81" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9508847594261169</v>
+        <v>0.9547396898269653</v>
       </c>
       <c r="F81" t="n">
-        <v>0.02718950808048248</v>
+        <v>0.04638580977916718</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3497,10 +3509,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.9442794919013977</v>
+        <v>0.9408166408538818</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3725075721740723</v>
+        <v>0.3591372966766357</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3518,16 +3530,16 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D82" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9667975902557373</v>
+        <v>0.9717509150505066</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1389621198177338</v>
+        <v>0.2503550052642822</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3535,10 +3547,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.9142664074897766</v>
+        <v>0.9122791886329651</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1181094869971275</v>
+        <v>0.1266481727361679</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3556,16 +3568,16 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D83" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9828101992607117</v>
+        <v>0.9822400808334351</v>
       </c>
       <c r="F83" t="n">
-        <v>0.6275185346603394</v>
+        <v>0.6250250935554504</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3573,14 +3585,14 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.8692582845687866</v>
+        <v>0.9004362225532532</v>
       </c>
       <c r="I83" t="n">
-        <v>0.02138357609510422</v>
+        <v>0.08167202770709991</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3594,16 +3606,16 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D84" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9872398376464844</v>
+        <v>0.9852071404457092</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8323942422866821</v>
+        <v>0.7609779834747314</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3611,10 +3623,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.9192852973937988</v>
+        <v>0.907864511013031</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1436202079057693</v>
+        <v>0.1075053587555885</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3632,16 +3644,16 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D85" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E85" t="n">
-        <v>0.972489058971405</v>
+        <v>0.9756034016609192</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2475676089525223</v>
+        <v>0.3594341576099396</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3649,14 +3661,14 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.8799092173576355</v>
+        <v>0.9459896087646484</v>
       </c>
       <c r="I85" t="n">
-        <v>0.03168955445289612</v>
+        <v>0.4289301633834839</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3670,27 +3682,27 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D86" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9578579664230347</v>
+        <v>0.9535247087478638</v>
       </c>
       <c r="F86" t="n">
-        <v>0.05527007579803467</v>
+        <v>0.04114263877272606</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.8515787720680237</v>
+        <v>0.8455844521522522</v>
       </c>
       <c r="I86" t="n">
-        <v>0.01133662834763527</v>
+        <v>0.01173908356577158</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3708,16 +3720,16 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D87" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E87" t="n">
-        <v>0.965970516204834</v>
+        <v>0.9622807502746582</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1276214271783829</v>
+        <v>0.09828916192054749</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3725,10 +3737,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.9578964114189148</v>
+        <v>0.9620459079742432</v>
       </c>
       <c r="I87" t="n">
-        <v>0.592339813709259</v>
+        <v>0.6990393996238708</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3746,16 +3758,16 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D88" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9707619547843933</v>
+        <v>0.9690312147140503</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2082242965698242</v>
+        <v>0.1921893507242203</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3763,10 +3775,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.9472247958183289</v>
+        <v>0.9554510116577148</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4141338765621185</v>
+        <v>0.5805972218513489</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3784,16 +3796,16 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D89" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9752354025840759</v>
+        <v>0.9775435328483582</v>
       </c>
       <c r="F89" t="n">
-        <v>0.323885589838028</v>
+        <v>0.4274614751338959</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3801,14 +3813,14 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.9131455421447754</v>
+        <v>0.8864523768424988</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1130642518401146</v>
+        <v>0.04896741360425949</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -3822,16 +3834,16 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D90" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9839653372764587</v>
+        <v>0.9833688735961914</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6823610663414001</v>
+        <v>0.676908016204834</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3839,10 +3851,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.9379855990409851</v>
+        <v>0.9487780332565308</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2950707674026489</v>
+        <v>0.4705794155597687</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3860,16 +3872,16 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D91" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E91" t="n">
-        <v>0.9768334627151489</v>
+        <v>0.975070059299469</v>
       </c>
       <c r="F91" t="n">
-        <v>0.3767770528793335</v>
+        <v>0.3422987461090088</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3877,10 +3889,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.9031859636306763</v>
+        <v>0.9101682901382446</v>
       </c>
       <c r="I91" t="n">
-        <v>0.07680828869342804</v>
+        <v>0.1170998588204384</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3898,16 +3910,16 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D92" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9385418891906738</v>
+        <v>0.9460411071777344</v>
       </c>
       <c r="F92" t="n">
-        <v>0.008106667548418045</v>
+        <v>0.01985653676092625</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3915,10 +3927,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0.7850464582443237</v>
+        <v>0.7851274013519287</v>
       </c>
       <c r="I92" t="n">
-        <v>0.001274504931643605</v>
+        <v>0.001740044564940035</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -3936,16 +3948,16 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D93" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E93" t="n">
-        <v>0.912880539894104</v>
+        <v>0.9198935627937317</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0008119586855173111</v>
+        <v>0.001857839641161263</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3953,14 +3965,14 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0.9087762832641602</v>
+        <v>0.8780551552772522</v>
       </c>
       <c r="I93" t="n">
-        <v>0.09539134055376053</v>
+        <v>0.03619485720992088</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -3974,16 +3986,16 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D94" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E94" t="n">
-        <v>0.94404536485672</v>
+        <v>0.9471572637557983</v>
       </c>
       <c r="F94" t="n">
-        <v>0.01379387732595205</v>
+        <v>0.02210781536996365</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3991,10 +4003,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0.8392277956008911</v>
+        <v>0.8241023421287537</v>
       </c>
       <c r="I94" t="n">
-        <v>0.00737834582105279</v>
+        <v>0.005796815268695354</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4012,16 +4024,16 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D95" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9762811660766602</v>
+        <v>0.9713205695152283</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3577690422534943</v>
+        <v>0.240190327167511</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4029,10 +4041,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>0.9574434757232666</v>
+        <v>0.9469312429428101</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5840368270874023</v>
+        <v>0.4426857829093933</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4050,16 +4062,16 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D96" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E96" t="n">
-        <v>0.8998362421989441</v>
+        <v>0.9035887718200684</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0002797936031129211</v>
+        <v>0.0004879921034444124</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4067,10 +4079,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>0.8935132622718811</v>
+        <v>0.8960400819778442</v>
       </c>
       <c r="I96" t="n">
-        <v>0.05296370759606361</v>
+        <v>0.0694725438952446</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4088,16 +4100,16 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D97" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9377049207687378</v>
+        <v>0.9401580095291138</v>
       </c>
       <c r="F97" t="n">
-        <v>0.007485989946871996</v>
+        <v>0.0113655086606741</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4105,10 +4117,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>0.8873747587203979</v>
+        <v>0.8810697793960571</v>
       </c>
       <c r="I97" t="n">
-        <v>0.04194623604416847</v>
+        <v>0.04032380878925323</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -4126,16 +4138,16 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D98" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9431594610214233</v>
+        <v>0.9483034014701843</v>
       </c>
       <c r="F98" t="n">
-        <v>0.01265128329396248</v>
+        <v>0.02469737827777863</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4143,10 +4155,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0.9446248412132263</v>
+        <v>0.9320944547653198</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3772075474262238</v>
+        <v>0.2630972266197205</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4164,16 +4176,16 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D99" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E99" t="n">
-        <v>0.9506118297576904</v>
+        <v>0.9407841563224792</v>
       </c>
       <c r="F99" t="n">
-        <v>0.02645371295511723</v>
+        <v>0.01205278746783733</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4181,14 +4193,14 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>0.925222635269165</v>
+        <v>0.8682929873466492</v>
       </c>
       <c r="I99" t="n">
-        <v>0.180928647518158</v>
+        <v>0.02561072818934917</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4202,27 +4214,27 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D100" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9556047916412354</v>
+        <v>0.9629071354866028</v>
       </c>
       <c r="F100" t="n">
-        <v>0.04387835413217545</v>
+        <v>0.1046363115310669</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.8717948794364929</v>
+        <v>0.8712231516838074</v>
       </c>
       <c r="I100" t="n">
-        <v>0.02346634492278099</v>
+        <v>0.028394415974617</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4240,16 +4252,16 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D101" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9610931873321533</v>
+        <v>0.9585435390472412</v>
       </c>
       <c r="F101" t="n">
-        <v>0.07712908834218979</v>
+        <v>0.06767860800027847</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4257,10 +4269,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.9618384838104248</v>
+        <v>0.9560087323188782</v>
       </c>
       <c r="I101" t="n">
-        <v>0.6662582159042358</v>
+        <v>0.5903500318527222</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4278,16 +4290,16 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D102" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E102" t="n">
-        <v>0.9177281856536865</v>
+        <v>0.912024974822998</v>
       </c>
       <c r="F102" t="n">
-        <v>0.001227126340381801</v>
+        <v>0.0009623119840398431</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4295,10 +4307,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>0.8058314323425293</v>
+        <v>0.8520317077636719</v>
       </c>
       <c r="I102" t="n">
-        <v>0.002441393677145243</v>
+        <v>0.01459719333797693</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4316,16 +4328,16 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D103" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9725508093833923</v>
+        <v>0.9781302809715271</v>
       </c>
       <c r="F103" t="n">
-        <v>0.2490927129983902</v>
+        <v>0.449766606092453</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4333,10 +4345,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0.9685614109039307</v>
+        <v>0.9695866703987122</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7927655577659607</v>
+        <v>0.8318690657615662</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4354,16 +4366,16 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D104" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E104" t="n">
-        <v>0.9407117366790771</v>
+        <v>0.9456968903541565</v>
       </c>
       <c r="F104" t="n">
-        <v>0.009980687871575356</v>
+        <v>0.01921152323484421</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4371,10 +4383,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0.797139048576355</v>
+        <v>0.8190232515335083</v>
       </c>
       <c r="I104" t="n">
-        <v>0.001853951485827565</v>
+        <v>0.004928334150463343</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4392,27 +4404,27 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D105" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E105" t="n">
-        <v>0.9521393179893494</v>
+        <v>0.9799374938011169</v>
       </c>
       <c r="F105" t="n">
-        <v>0.03085511364042759</v>
+        <v>0.5231719017028809</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.9215713143348694</v>
+        <v>0.9096788167953491</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1569909751415253</v>
+        <v>0.1149915754795074</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4430,16 +4442,16 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D106" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9688373208045959</v>
+        <v>0.9634416699409485</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1712662279605865</v>
+        <v>0.1103745847940445</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4447,10 +4459,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>0.9101682305335999</v>
+        <v>0.9019039869308472</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1006945073604584</v>
+        <v>0.08621858060359955</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4468,16 +4480,16 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D107" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E107" t="n">
-        <v>0.9824406504631042</v>
+        <v>0.9851836562156677</v>
       </c>
       <c r="F107" t="n">
-        <v>0.6101530790328979</v>
+        <v>0.7599226832389832</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4485,14 +4497,14 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>0.8988144993782043</v>
+        <v>0.8847172856330872</v>
       </c>
       <c r="I107" t="n">
-        <v>0.06489373743534088</v>
+        <v>0.04598746076226234</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4506,27 +4518,27 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D108" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E108" t="n">
-        <v>0.9502930045127869</v>
+        <v>0.9564782977104187</v>
       </c>
       <c r="F108" t="n">
-        <v>0.02562015689909458</v>
+        <v>0.0551079586148262</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>0.9297195076942444</v>
+        <v>0.9093002080917358</v>
       </c>
       <c r="I108" t="n">
-        <v>0.215303510427475</v>
+        <v>0.1133870109915733</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4544,16 +4556,16 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D109" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E109" t="n">
-        <v>0.8935235738754272</v>
+        <v>0.9049277305603027</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0001708704512566328</v>
+        <v>0.0005425761919468641</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4561,10 +4573,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0.9644534587860107</v>
+        <v>0.963129460811615</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7160541415214539</v>
+        <v>0.7187622785568237</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4582,16 +4594,16 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D110" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E110" t="n">
-        <v>0.9822426438331604</v>
+        <v>0.9757969975471497</v>
       </c>
       <c r="F110" t="n">
-        <v>0.6009095311164856</v>
+        <v>0.3658213317394257</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4599,10 +4611,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.9245228171348572</v>
+        <v>0.9249728918075562</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1760800182819366</v>
+        <v>0.2027287781238556</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4620,16 +4632,16 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D111" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9251474738121033</v>
+        <v>0.9143773317337036</v>
       </c>
       <c r="F111" t="n">
-        <v>0.002353280084207654</v>
+        <v>0.001168481074273586</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4637,10 +4649,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>0.9445332884788513</v>
+        <v>0.9379718899726868</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3759572505950928</v>
+        <v>0.324909508228302</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -4658,16 +4670,16 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D112" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E112" t="n">
-        <v>0.9589847326278687</v>
+        <v>0.9691215753555298</v>
       </c>
       <c r="F112" t="n">
-        <v>0.06205995008349419</v>
+        <v>0.1939006149768829</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4675,14 +4687,14 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>0.7640789747238159</v>
+        <v>0.9343229532241821</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0006798615795560181</v>
+        <v>0.2851709425449371</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -4696,16 +4708,16 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D113" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9377968907356262</v>
+        <v>0.9345468878746033</v>
       </c>
       <c r="F113" t="n">
-        <v>0.007551694754511118</v>
+        <v>0.006764968857169151</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4713,14 +4725,14 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>0.9355443716049194</v>
+        <v>0.8778311014175415</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2690709233283997</v>
+        <v>0.03590618818998337</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4734,16 +4746,16 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D114" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E114" t="n">
-        <v>0.8888018131256104</v>
+        <v>0.9000066518783569</v>
       </c>
       <c r="F114" t="n">
-        <v>0.000119219817861449</v>
+        <v>0.000368622422683984</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4751,10 +4763,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0.8296331167221069</v>
+        <v>0.8238672018051147</v>
       </c>
       <c r="I114" t="n">
-        <v>0.005326374433934689</v>
+        <v>0.00575321214273572</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -4772,16 +4784,16 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D115" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E115" t="n">
-        <v>0.9789286851882935</v>
+        <v>0.9809219837188721</v>
       </c>
       <c r="F115" t="n">
-        <v>0.4558582305908203</v>
+        <v>0.5657927393913269</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4789,10 +4801,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.9149064421653748</v>
+        <v>0.9402812123298645</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1210915669798851</v>
+        <v>0.3524729013442993</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -4810,16 +4822,16 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D116" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E116" t="n">
-        <v>0.9426209330558777</v>
+        <v>0.9507474303245544</v>
       </c>
       <c r="F116" t="n">
-        <v>0.01200549118220806</v>
+        <v>0.0313265472650528</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4827,10 +4839,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.928787887096405</v>
+        <v>0.9182969331741333</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2077042311429977</v>
+        <v>0.1583592295646667</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -4848,16 +4860,16 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D117" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E117" t="n">
-        <v>0.9795864224433899</v>
+        <v>0.9784799218177795</v>
       </c>
       <c r="F117" t="n">
-        <v>0.4828747510910034</v>
+        <v>0.4634281396865845</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4865,10 +4877,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>0.9337935447692871</v>
+        <v>0.9333387017250061</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2517250776290894</v>
+        <v>0.2752221822738647</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -4886,16 +4898,16 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D118" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E118" t="n">
-        <v>0.9611021280288696</v>
+        <v>0.9589652419090271</v>
       </c>
       <c r="F118" t="n">
-        <v>0.07720045745372772</v>
+        <v>0.07058496028184891</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4903,10 +4915,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>0.920908510684967</v>
+        <v>0.8943780064582825</v>
       </c>
       <c r="I118" t="n">
-        <v>0.152992382645607</v>
+        <v>0.06536432355642319</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -4924,16 +4936,16 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D119" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E119" t="n">
-        <v>0.9580698609352112</v>
+        <v>0.9612952470779419</v>
       </c>
       <c r="F119" t="n">
-        <v>0.05648653581738472</v>
+        <v>0.08907182514667511</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4941,10 +4953,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>0.9465334415435791</v>
+        <v>0.9503340125083923</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4040493667125702</v>
+        <v>0.4949971735477448</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -4962,16 +4974,16 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D120" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8969770669937134</v>
+        <v>0.8833345770835876</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0002233997220173478</v>
+        <v>0.0001057098124874756</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4979,10 +4991,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>0.9001349210739136</v>
+        <v>0.8904510140419006</v>
       </c>
       <c r="I120" t="n">
-        <v>0.06827698647975922</v>
+        <v>0.05662615224719048</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -5000,16 +5012,16 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D121" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E121" t="n">
-        <v>0.9756013154983521</v>
+        <v>0.9801082015037537</v>
       </c>
       <c r="F121" t="n">
-        <v>0.3354286551475525</v>
+        <v>0.5304417610168457</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5017,10 +5029,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>0.8731861114501953</v>
+        <v>0.8692402839660645</v>
       </c>
       <c r="I121" t="n">
-        <v>0.02469847351312637</v>
+        <v>0.02647781372070312</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
